--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358081</v>
+        <v>123358022</v>
       </c>
       <c r="B2" t="n">
-        <v>58156</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,19 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345149</v>
+        <v>345132</v>
       </c>
       <c r="R2" t="n">
-        <v>6535556</v>
+        <v>6535541</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,6 +761,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358022</v>
+        <v>123357209</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>100634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,31 +809,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345132</v>
+        <v>345198</v>
       </c>
       <c r="R3" t="n">
-        <v>6535541</v>
+        <v>6535500</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
+          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123357209</v>
+        <v>123358081</v>
       </c>
       <c r="B4" t="n">
-        <v>100631</v>
+        <v>58159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,27 +935,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -973,13 +978,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345198</v>
+        <v>345149</v>
       </c>
       <c r="R4" t="n">
-        <v>6535500</v>
+        <v>6535556</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,11 +1014,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>123357209</v>
       </c>
       <c r="B3" t="n">
-        <v>100634</v>
+        <v>100636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358022</v>
+        <v>123357209</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>100642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345132</v>
+        <v>345198</v>
       </c>
       <c r="R2" t="n">
-        <v>6535541</v>
+        <v>6535500</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
+          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123357209</v>
+        <v>123358022</v>
       </c>
       <c r="B3" t="n">
-        <v>100636</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,31 +809,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345198</v>
+        <v>345132</v>
       </c>
       <c r="R3" t="n">
-        <v>6535500</v>
+        <v>6535541</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I grandominerad skog med stort inslag av asp.</t>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123357209</v>
+        <v>123358081</v>
       </c>
       <c r="B2" t="n">
-        <v>100645</v>
+        <v>58165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,13 +734,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345198</v>
+        <v>345149</v>
       </c>
       <c r="R2" t="n">
-        <v>6535500</v>
+        <v>6535556</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,11 +770,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358081</v>
+        <v>123357209</v>
       </c>
       <c r="B3" t="n">
-        <v>58159</v>
+        <v>100662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,36 +817,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -856,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345149</v>
+        <v>345198</v>
       </c>
       <c r="R3" t="n">
-        <v>6535556</v>
+        <v>6535500</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,6 +887,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -926,7 +926,7 @@
         <v>123358022</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358081</v>
+        <v>123357209</v>
       </c>
       <c r="B2" t="n">
-        <v>58165</v>
+        <v>100680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345149</v>
+        <v>345198</v>
       </c>
       <c r="R2" t="n">
-        <v>6535556</v>
+        <v>6535500</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,6 +761,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123357209</v>
+        <v>123358022</v>
       </c>
       <c r="B3" t="n">
-        <v>100662</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,31 +809,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345198</v>
+        <v>345132</v>
       </c>
       <c r="R3" t="n">
-        <v>6535500</v>
+        <v>6535541</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I grandominerad skog med stort inslag av asp.</t>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123358022</v>
+        <v>123358081</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>58168</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,10 +952,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -973,13 +978,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345132</v>
+        <v>345149</v>
       </c>
       <c r="R4" t="n">
-        <v>6535541</v>
+        <v>6535556</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,11 +1014,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123357209</v>
+        <v>123358081</v>
       </c>
       <c r="B2" t="n">
-        <v>100680</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,13 +734,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345198</v>
+        <v>345149</v>
       </c>
       <c r="R2" t="n">
-        <v>6535500</v>
+        <v>6535556</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,11 +770,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,7 +804,7 @@
         <v>123358022</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123358081</v>
+        <v>123357209</v>
       </c>
       <c r="B4" t="n">
-        <v>58168</v>
+        <v>100682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,36 +939,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -978,13 +973,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345149</v>
+        <v>345198</v>
       </c>
       <c r="R4" t="n">
-        <v>6535556</v>
+        <v>6535500</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,6 +1009,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358081</v>
+        <v>123358022</v>
       </c>
       <c r="B2" t="n">
-        <v>58169</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,19 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345149</v>
+        <v>345132</v>
       </c>
       <c r="R2" t="n">
-        <v>6535556</v>
+        <v>6535541</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,6 +761,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358022</v>
+        <v>123358081</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,10 +830,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345132</v>
+        <v>345149</v>
       </c>
       <c r="R3" t="n">
-        <v>6535541</v>
+        <v>6535556</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,11 +892,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,7 +926,7 @@
         <v>123357209</v>
       </c>
       <c r="B4" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358081</v>
+        <v>123357209</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,36 +813,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -856,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345149</v>
+        <v>345198</v>
       </c>
       <c r="R3" t="n">
-        <v>6535556</v>
+        <v>6535500</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,6 +883,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123357209</v>
+        <v>123358081</v>
       </c>
       <c r="B4" t="n">
-        <v>100257</v>
+        <v>58169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,27 +935,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -973,13 +978,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345198</v>
+        <v>345149</v>
       </c>
       <c r="R4" t="n">
-        <v>6535500</v>
+        <v>6535556</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,11 +1014,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123357209</v>
+        <v>123358081</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,27 +813,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -847,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345198</v>
+        <v>345149</v>
       </c>
       <c r="R3" t="n">
-        <v>6535500</v>
+        <v>6535556</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,11 +892,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +905,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123358081</v>
+        <v>123357209</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,36 +939,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -978,13 +973,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345149</v>
+        <v>345198</v>
       </c>
       <c r="R4" t="n">
-        <v>6535556</v>
+        <v>6535500</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,6 +1009,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358022</v>
+        <v>123357209</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345132</v>
+        <v>345198</v>
       </c>
       <c r="R2" t="n">
-        <v>6535541</v>
+        <v>6535500</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
+          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123357209</v>
+        <v>123358022</v>
       </c>
       <c r="B4" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +935,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345198</v>
+        <v>345132</v>
       </c>
       <c r="R4" t="n">
-        <v>6535500</v>
+        <v>6535541</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I grandominerad skog med stort inslag av asp.</t>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 9332-2025 artfynd.xlsx
+++ b/artfynd/A 9332-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123357209</v>
+        <v>123358081</v>
       </c>
       <c r="B2" t="n">
-        <v>100257</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,13 +734,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345198</v>
+        <v>345149</v>
       </c>
       <c r="R2" t="n">
-        <v>6535500</v>
+        <v>6535556</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,11 +770,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358081</v>
+        <v>123358022</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,19 +834,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -856,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345149</v>
+        <v>345132</v>
       </c>
       <c r="R3" t="n">
-        <v>6535556</v>
+        <v>6535541</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,6 +887,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123358022</v>
+        <v>123357209</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +935,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345132</v>
+        <v>345198</v>
       </c>
       <c r="R4" t="n">
-        <v>6535541</v>
+        <v>6535500</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
+          <t>I grandominerad skog med stort inslag av asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
